--- a/public/template/firefighters_template.xlsx
+++ b/public/template/firefighters_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\program\clothing-management-system\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4CF1A3-4DA0-4272-9A34-0A14A773F1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCC920D-3673-4DEC-84BA-438E12D4F5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>编号</t>
   </si>
@@ -155,6 +155,14 @@
   </si>
   <si>
     <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可用余额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -555,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL4"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -575,11 +583,13 @@
     <col min="32" max="32" width="10.4140625" style="1" customWidth="1"/>
     <col min="33" max="33" width="11.58203125" style="1" customWidth="1"/>
     <col min="34" max="34" width="11.75" style="1" customWidth="1"/>
-    <col min="35" max="37" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.6640625" style="1"/>
+    <col min="35" max="36" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.83203125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>37</v>
       </c>
@@ -619,8 +629,9 @@
       <c r="AI1" s="9"/>
       <c r="AJ1" s="9"/>
       <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
     </row>
-    <row r="2" spans="1:38" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" ht="14" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -730,10 +741,13 @@
         <v>35</v>
       </c>
       <c r="AK2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL2" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -843,13 +857,16 @@
         <v>36</v>
       </c>
       <c r="AK3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="AL3" s="2">
         <v>37</v>
       </c>
-      <c r="AL3" s="4" t="s">
+      <c r="AM3" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>2</v>
       </c>
@@ -958,13 +975,16 @@
       <c r="AJ4" s="6">
         <v>36</v>
       </c>
-      <c r="AK4" s="2" t="s">
+      <c r="AK4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL4" s="2" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="A1:AL1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
